--- a/eval/nbfc_retrieval_test_questions_results_v2.xlsx
+++ b/eval/nbfc_retrieval_test_questions_results_v2.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The asset-size threshold for a non-deposit-taking NBFC to be placed in the Middle Layer is ₹1,000 crore [1], [2], [3]. This applies regardless of temporary fluctuations in asset size [2], and even if the NBFC's size falls below ₹1,000 crore temporarily, it remains subject to Middle Layer regulations until the next audited balance sheet is submitted [2]. Additionally, for groups with consolidated assets of ₹1,000 crore or more, individual NBFCs within the group are classified as Middle Layer entities [4].</t>
+          <t>The asset-size threshold placing a non-deposit-taking NBFC in the Middle Layer under scale-based regulation is ₹1,000 crore. This is explicitly stated in [1], which includes non-deposit taking NBFCs with asset size of ₹1,000 crore and above in the Middle Layer. Additionally, [2] confirms that once an NBFC reaches this threshold, it is subject to Middle Layer regulatory requirements. Note that existing NBFC-ND-SI with asset size between ₹500 crore and ₹1,000 crore (excluding those in the Middle Layer) are classified as NBFC-BL (Base Layer) per [3].</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7.3</v>
+        <v>10.1</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -564,11 +564,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The minimum capital to risk-weighted assets ratio (CRAR) for a Middle Layer NBFC is **15 per cent** of the aggregate RWAs [1]. Of this, the **minimum Tier 1 capital** required is **10 per cent** of the aggregate RWAs [1]. The Tier 2 capital may not exceed **100 per cent of Tier 1 capital** [1]. 
-**Conditions and limitations**:  
-- The Tier 2 capital is part of the CRAR but cannot surpass 100% of Tier 1 capital.  
-- The CRAR minimum of 15% is achieved by combining Tier 1 (minimum 10%) and Tier 2 (up to 10% of Tier 1).  
-- This applies specifically to NBFCs in the Middle Layer and above, excluding other categories like NBFCs-D, NBFCs-ND, or NBFC-MFIs [1][2][4].</t>
+          <t>The minimum capital to risk-weighted assets ratio (CRAR) for a Middle Layer NBFC is **15 per cent of the aggregate RWAs** [1]. The Tier 1 capital requirement for such NBFCs is **10 per cent of the aggregate RWAs** [1]. The Tier 2 capital may not exceed **100 per cent of Tier 1 capital** [1]. Thus, the CRAR of 15% includes Tier 1 (10%) and Tier 2 (up to 10%, but adjusted to meet the 15% total).</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -587,7 +583,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16.9</v>
+        <v>20.7</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -621,7 +617,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>An Upper Layer NBFC (NBFC - UL) must maintain a minimum Common Equity Tier 1 (CET1) capital of **9 per cent of the aggregate RWAs** [1]. This requirement is explicitly stated in paragraph (4) of Chapter II Regulatory capital. No additional conditions or exceptions are specified for this ratio in the passages.</t>
+          <t>An Upper Layer NBFC (NBFC - UL) must maintain a minimum Common Equity Tier 1 (CET1) capital of **9 per cent of the aggregate RWAs** [1]. This requirement is explicitly stated in paragraph (4) of Chapter II Regulatory capital in the context. No other passage specifies a different CET1 ratio for NBFC-UL.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,7 +636,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -674,11 +670,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The minimum Net Owned Fund (NOF) required for an NBFC-ICC is ₹10 crore, which must be achieved by March 31, 2027.  
-**Conditions and timelines**:  
-- Existing NBFC-ICC with a current NOF of ₹2 crore must reach ₹5 crore by March 31, 2025, and ₹10 crore by March 31, 2027 [2].  
-- NBFCs failing to meet these milestones will lose eligibility for the Certificate of Registration (CoR) as NBFCs [2].  
-- This requirement applies to NBFC-ICC registered under the Factoring Regulation Act, as specified in the Reserve Bank of India (Non-Banking Financial Companies - Miscellaneous) Directions, 2025 [2].</t>
+          <t>The minimum Net Owned Fund (NOF) required for an NBFC-ICC is ₹10 crore, which must be achieved by March 31, 2027. Existing NBFC-ICC entities currently have a NOF of ₹2 crore and must progressively reach ₹5 crore by March 31, 2025, and ₹10 crore by March 31, 2027 [2].</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -697,7 +689,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -731,7 +723,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The minimum NOF for NBFC-P2P lending platforms and NBFC-Account Aggregators (NBFC-AA) is ₹2 crore [1]. This applies specifically to these categories as outlined in section 40 of the context passage. No additional conditions or exceptions are mentioned for these entities in the provided texts.</t>
+          <t>The minimum NOF for NBFC-P2P lending platforms is ₹2 crore [1]§40, and for NBFC-Account Aggregators (NBFC-AA), it is also ₹2 crore [1]§40. These figures are explicitly stated in the context passages.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -750,7 +742,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -784,13 +776,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>After the glide path ended (March 31, 2026), an overdue period of **more than 90 days** triggers NPA classification for a Base Layer NBFC [1]. 
-**Conditions and exceptions**:  
-- The 90-day threshold applies to NBFCs not already following the 90-day norm [1].  
-- For NBFC-ML (Middle Layer), the NPA classification is also based on 90 days overdue [5].  
-- The glide path timelines (e.g., 150 days by 2024, 120 days by 2025) are no longer applicable after March 31, 2026 [1].  
-- For NBFC-Factors with asset size ≥ ₹500 crore, the NPA norm is 90 days, but this is specific to factoring regulations [2].  
-- The day-end process determines the exact classification date, with SMA/NPA tags applied based on overdue days [4].</t>
+          <t>After the glide path ended on March 31, 2026, the NPA classification for a Base Layer NBFC is triggered by an overdue period of **more than 90 days** [1]. This applies to NBFCs that were part of the glide path transition from 180-day to 90-day norms. The 90-day threshold is specified in the glide path timeline for applicable NBFCs [1].</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -800,16 +786,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>all key figures present (31, 2026, 90days, 150days, 2024, 120days)</t>
+          <t>found 31, 2026, 90days; missing 150days, 2024, 120days</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -843,13 +829,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The provisioning requirement for sub-standard assets is a general provision of **10 per cent of the total outstanding** as specified in [4] and [5]. 
-**Conditions and exceptions**:  
-1. **Mortgage Guarantee Companies (MGCs)**: Sub-standard assets require a general provision of 10% of total outstanding, as per [4].  
-2. **NBFCs**: Sub-standard assets are covered under provisioning norms for NPAs, requiring a 10% provision, as stated in [5].  
-3. **Renegotiated/Rescheduled Assets**: If a hire purchase/leased asset is renegotiated or rescheduled, it may be classified as sub-standard, and provisions must be made as applicable to such assets, though the exact rate is not specified in [1].  
-4. **Project Finance**: Sub-standard assets in project finance are governed by general provisioning rates (10%) unless financial closure was achieved by October 1, 2025, in which case prior guidelines apply, as per [5].  
-Other contexts (e.g., [2]) mention provisions against sub-standard assets but do not specify the rate, relying on broader norms.</t>
+          <t>The provisioning requirement for sub-standard assets is a general provision of **10 per cent of the total outstanding**. This applies to:  
+- **Housing Finance Companies (HFCs)** as per paragraph 47 of [3], which references paragraph 29 of the RBI Directions, 2025 [2], and  
+- **NBFCs** as specified in [5] section 32(1), which explicitly states "Sub-standard assets - A general provision of ten per cent of total outstanding shall be made."  
+For **mortgage guarantee assets** classified as sub-standard, the same 10% provision applies [4](iii).  
+No exceptions or additional rates are mentioned for sub-standard assets in the passages.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,16 +843,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>all key figures present (10%)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -902,11 +886,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The standard asset provisioning rate for Middle Layer NBFCs (NBFC-ML) is **0.40 per cent of the outstanding** [1]. This rate applies to all standard assets, including microfinance loans [1]. 
-Conditions and exceptions:  
-- The provisioning for NBFC-ML is in addition to instructions in paragraphs 28–36 [1].  
-- For housing loans extended at teaser rates, the rate is 2.00 per cent initially, decreasing to 0.40 per cent after one year if rates reset to higher levels and the account remains 'standard' [2].  
-- NBFC-ML must follow paragraphs 28 and 55 of the RBI Directions, 2025, which include this 0.40 per cent rate [5].</t>
+          <t>The standard asset provisioning rate for Middle Layer NBFCs (NBFC-ML) is **0.40 per cent of the outstanding** [1]. This rate applies to all standard assets, including microfinance loans [1]. Additionally, Middle Layer CICs (Core Investment Companies) follow this rate as per paragraph 55 of the RBI directions [5]. No other rates or exceptions are specified for NBFC-ML in the passages.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -925,7 +905,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -959,14 +939,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The KYC periodic updation frequencies are:  
-- **High-risk customers**: Every **2 years** [1].  
-- **Medium-risk customers**: Every **8 years** [1].  
-- **Low-risk customers**: Every **10 years** from the date of account opening or last KYC updation [1].  
-**Exceptions/Conditions**:  
-1. For **low-risk individual customers**, updation is allowed within **1 year of the due date** or **June 30, 2026**, whichever is later [1].  
-2. The NBFC must document its policy for periodic updation in its internal KYC policy, approved by the Board of Directors or delegated committee [1].  
-3. For **non-individual customers**, additional measures (e.g., verifying PAN, ensuring documents meet current CDD standards) apply during periodic updation [3].</t>
+          <t>The periodic KYC update frequencies are as follows:  
+- **High-risk customers**: At least once every **2 years** [1].  
+- **Medium-risk customers**: At least once every **8 years** [1].  
+- **Low-risk customers**: At least once every **10 years** [1].  
+For **low-risk individual customers**, an exception applies: KYC must be updated within **1 year of its falling due** or by **June 30, 2026**, whichever is later [1]. This exception also applies to low-risk customers whose periodic KYC updation had already fallen due.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -985,7 +962,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1019,13 +996,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Customer identification and transaction records must be preserved for **five years** from the date of the transaction for transaction records [1](1), and **five years after the business relationship has ended** for customer identification records [1](2). Records must be maintained in hard or soft format [1](7). 
-**Conditions and exceptions**:  
-- Transaction records must include details like nature of transactions, amounts, dates, and parties [1](5)(i)-(iv).  
-- For non-profit organization customers, registration details on the DARPAN Portal must be retained for five years post-relationship or account closure [1](48).  
-- Periodic KYC updates must be completed within 30 days of document changes, with advance intimations and reminders [3](42).  
-- Temporary account suspension may occur if PAN/e-document is not provided, but accounts for disabled or elderly customers may have relaxed policies [3](43).  
-- KYC identifiers from CKYCR must be used for verification, unless there is a change in customer data, incomplete records, expired documents, or enhanced due diligence needs [6](9).</t>
+          <t>The customer identification and transaction records must be preserved for **at least five years from the date of the transaction** [1], and **five years after the business relationship has ended** [1]. Additionally, for non-profit organisation customers, registration records must be maintained for **five years after the business relationship ends or the account is closed**, whichever is later [1]. These periods apply to both identification records and transaction data.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1035,16 +1006,16 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>no numeric facts to compare - read the answer yourself</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1078,11 +1049,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The timeline for filing a Suspicious Transaction Report (STR) with FIU-IND is not explicitly specified in the provided passages. However, the following conditions apply:  
-1. **Delays in reporting**: A delay of each day in not reporting a transaction or rectifying a mis-represented transaction beyond the time limit specified in Rule 7 of the PML (Maintenance of Records) Rules, 2005 constitutes a separate violation [1].  
-2. **Mandatory filing**: NBFCs, banks, and other entities must file an STR with FIU-IND **immediately** upon identifying suspicious transactions (e.g., matches with designated individuals/entities under UAPA provisions) [2].  
-3. **Wire transfer requirements**: For wire transfers lacking required originator/beneficiary information, STRs must be filed **in accordance with the PML Rules** if the transaction is found suspicious [3].  
-No specific numerical deadlines (e.g., days or dates) are provided in the passages for STR filing, relying instead on adherence to procedural rules and immediate action upon detection of suspicious activity.</t>
+          <t>The context passages do not specify a precise timeline for filing a Suspicious Transaction Report (STR) with FIU-IND. However, they outline the following conditions and requirements:  
+- **Mandatory Filing**: NBFCs must file STRs for suspicious transactions detected in accordance with the PML Rules [1][3].  
+- **Penalties for Delays**: A delay of each day in reporting a transaction or rectifying a mis-represented transaction beyond the specified time limit constitutes a separate violation [1][51].  
+- **Specific Scenarios**: For matches with designated individuals/entities, STRs must be filed immediately upon identification of such transactions [2][5.1(v)].  
+- **Technological Compliance**: NBFCs must use electronic utilities or tools provided by FIU-IND to file STRs, with no restrictions on operations based solely on STR filings [1][50].  
+No explicit deadline or timeframe for filing STRs is provided in the passages.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1092,16 +1064,16 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>no numeric facts to compare - read the answer yourself</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10.6</v>
+        <v>9</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1135,11 +1107,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The minimum tenure for public deposits accepted by an NBFC is twelve months, and the maximum is sixty months, as stipulated in [5].  
-**Conditions**:  
-- Deposits must be repayable **after a period of twelve months** (minimum) **but not later than sixty months** (maximum) from the date of acceptance or renewal [5].  
-- This applies to deposits accepted or renewed by NBFCs, excluding exceptions like unsecured debentures treated as non-public deposits [2].  
-- The tenure rules are part of the Reserve Bank of India (Non-Banking Financial Companies - Acceptance of Public Deposits) Directions, 2025 [5].</t>
+          <t>The minimum tenure for public deposits accepted by an NBFC is twelve months, and the maximum tenure is sixty months from the date of acceptance or renewal [5].</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1158,7 +1126,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1192,11 +1160,10 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The ceiling on public deposits an NBFC-D can hold relative to its NOF is **one and one-half times its NOF** [1].  
+          <t>The ceiling on public deposits an NBFC-D can hold relative to its NOF is **one and one-half times** its NOF [1].  
 **Conditions**:  
-1. If an NBFC holds public deposits exceeding this limit, it **shall not renew or accept fresh deposits** until it reaches the revised limit [1].  
-2. **Matured public deposits** cannot be renewed without the **express and voluntary consent of the depositor** [1].  
-3. This applies to NBFC-D registered with the RBI under the RBI Act, 1934 [6].</t>
+- If an NBFC holds public deposits exceeding this limit, it **shall not renew or accept fresh deposits** until it reaches the revised limit [1].  
+- **Matured public deposits** cannot be renewed without the **express and voluntary consent of the depositor** [1].</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1215,7 +1182,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1249,13 +1216,13 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The percentage of public deposits that an NBFC-D must maintain in liquid assets is **15%** [1].  
+          <t>The percentage of public deposits that an NBFC-D must maintain in liquid assets is **15%**. This is specified in Chapter-II of the Reserve Bank of India (Non-Banking Financial Companies - Acceptance of Public Deposits) Directions, 2025, where it states that NBFC-D shall invest in unencumbered approved securities valued at not less than 15% of the 'public deposit' outstanding [1]. 
 **Conditions and exceptions**:  
-- The 15% must be invested in unencumbered approved securities valued at no more than the current market price [1].  
-- NBFCs may invest **10%** in unencumbered approved securities and the remaining **5%** in term deposits with scheduled commercial banks, SIDBI, NABARD, or bonds issued by these entities [1].  
+- NBFCs may invest **10%** in unencumbered approved securities and the remaining **5%** in term deposits with specified institutions (scheduled commercial banks, SIDBI, NABARD) or bonds issued by these entities [1].  
 - The aggregate of investments in unencumbered approved securities, term deposits, and bonds must not be less than **15%** of public deposits [1].  
-- If public deposits decrease, NBFCs may withdraw a portion of securities proportionally, provided audited certification is submitted [1].  
-- Securities must maintain a market value not below the specified percentage of public deposits at all times [1].</t>
+- The market value of these securities must never fall below the specified percentage of public deposits at any time [1].  
+- NBFCs may withdraw securities proportionally to public deposit reductions, provided audited certification is submitted [1].  
+- Excess government securities held beyond requirements must be kept in separate accounts (SGL/gilt/dematerialized) for compliance purposes [5].</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1274,7 +1241,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1306,28 +1273,20 @@
           <t>high</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>The NBFC must pay compensation of ₹5,000 for each day of delay beyond 30 days after full repayment/ settlement of the loan, **if the delay is attributable to the NBFC** [1] §39, [2] §69. If the delay is not attributable to the NBFC, it must communicate reasons for the delay to the borrower [2] §69. Additionally, in cases of loss/damage to documents, the NBFC must bear associated costs and the delayed period penalty is calculated after a total period of 60 days (30 days for procedures + 30 days delay) [1] §40.</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.20 | 12942_Responsible-Business-Conduct.pdf p.24 | 12942_Responsible-Business-Conduct.pdf p.19 | 12942_Responsible-Business-Conduct.pdf p.14 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12943_Know-Your-Customer.pdf p.34</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>all key figures present (30days, 5000)</t>
+          <t>ReadTimeout: timed out</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9.9</v>
+        <v>300.6</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1361,13 +1320,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The cap on Default Loss Guarantee (DLG) cover in digital lending is **five per cent of the total amount disbursed** from the loan portfolio under a DLG arrangement. This is specified in Rule 24(1) of the Reserve Bank of India (Non-Banking Financial Companies - Credit Facilities) Directions, 2025 [1]. 
-**Conditions and limitations**:  
-1. The DLG cover is calculated proportionally to the disbursed amount of the fixed "DLG set" portfolio [1]. For example, if a portfolio of ₹40 crore is earmarked, the DLG cover is ₹2 crore (5% of ₹40 crore), which activates as loans are disbursed [1].  
-2. If the DLG is invoked (e.g., due to defaults), the available cover reduces by the invoked amount, and the remaining cover is recalculated based on the updated disbursed amount [2].  
-3. Recovery of defaulted loans does not reinstate the DLG cover once it has been exhausted [2].  
-4. The cap applies to all NBFCs, including those engaged in digital lending, as digital lending is defined under the regulations but not subject to a separate DLG cap [5].  
-No explicit distinction is made between traditional lending and digital lending in the DLG cap rules.</t>
+          <t>The cap on Default Loss Guarantee (DLG) cover in digital lending is five per cent of the total amount disbursed out of the loan portfolio under the DLG arrangement. This is explicitly stated in [1], which mandates that the DLG cover cannot exceed 5% of the disbursed amount. For example, if a portfolio of ₹40 crore is earmarked, the DLG cover is fixed at ₹2 crore (5% of ₹40 crore), and as disbursements occur, the DLG cover adjusts proportionally to 5% of the disbursed amount [1]. This applies to digital lending as part of the broader NBFC framework, with no separate mention of a different cap for digital lending in the passages.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1377,16 +1330,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>all key figures present (5%)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1420,12 +1373,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The minimum cooling-off (look-up) period for digital loans is **one day**, as the NBFC must determine this period in their credit policy, ensuring it is **not less than one day** [1]. 
+          <t>The minimum cooling-off (look-up) period for digital loans is **one day**, as determined by the NBFC's credit policy. The borrower can exit the loan without penalty during this period, and the NBFC must ensure the period is not less than one day [1]. 
 **Conditions and exceptions**:  
-- The borrower can exit the loan during this period by paying the principal and proportionate APR without penalty.  
-- If the customer exits during the cooling-off period, the NBFC may retain a reasonable one-time processing fee, provided it is disclosed upfront in the Key Fact Statement (KFS) [1].  
-- For pre-payment beyond the cooling-off period, pre-payment rules under the RBI Directions, 2025, apply [1].  
-- The cooling-off period is distinct from post-default cooling periods for fresh exposures (which require a minimum of 12 months) [5].</t>
+- The cooling-off period is determined by the NBFC's board-approved policy but cannot be shorter than one day.  
+- If the borrower continues with the loan after the cooling-off period, pre-payment rules under the RBI Directions, 2025, apply [1].  
+- For digital loans, the cooling-off period is also referenced in the RE's board-approved policy, but the minimum remains one day [2].</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1444,7 +1396,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1478,18 +1430,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The credit concentration limits for a Middle Layer NBFC are:  
-- **25% of its Tier 1 capital** to a single party, and  
-- **40% of its Tier 1 capital** to a single group of parties.  
+          <t>The credit concentration limits for a Middle Layer NBFC are as follows:  
+- **Single party**: 25% of its Tier 1 capital [1].  
+- **Single group of parties**: 40% of its Tier 1 capital [1].  
+These limits may be exceeded by **5% for a single party** and **10% for a single group** if the additional exposure is due to infrastructure loans or investments [1].  
 **Exceptions**:  
-- The NBFC may exceed these limits by **5% for a single party** and **10% for a single group** if the additional exposure is for **infrastructure loans or investments** [1].  
-**Tier 1 Capital Calculation**:  
-- The applicable Tier 1 capital is determined based on the NBFC’s **latest available financial statements** (audited or subject to limited review) [1].  
-**Exemptions**:  
-- Exposure norms do not apply to investments in subsidiaries or companies in the same group, to the extent reduced from Owned Funds for NOF calculation [17].  
-- Exposures to the Government of India/State Governments (with zero risk weight) and fully government-guaranteed exposures are exempt [17].  
-**Policy Requirement**:  
-- The NBFC must formulate a Board-approved policy for managing exposures to single parties/groups [18].</t>
+1. Exposure norms **do not apply** to NBFCs not accessing public funds in India, either directly or indirectly, and not issuing guarantees [1].  
+2. Investments in subsidiaries or group companies (reduced from Owned Funds for NOF calculation) are exempt [1].  
+3. Exposures to the Government of India/State Governments (with zero risk weight) and fully government-guaranteed exposures are exempt [1].  
+**Note**: NBFC-IFC (Infrastructure Finance Companies) have higher limits (30% for a single party and 50% for a group) [1].</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1508,7 +1457,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14.2</v>
+        <v>18.7</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1542,7 +1491,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NBFCs must report credit information to credit information companies **monthly** for wilful defaulters [1] and large defaulters [2]. For structured digital lending products, reporting is required "irrespective of its nature / tenor" but without specifying a frequency [5]. Additionally, quarterly reporting is mandated for total exposure in specific credit risk transfer scenarios [4], but this pertains to a distinct reporting requirement.</t>
+          <t>NBFCs must report credit information to credit information companies **monthly** for wilful defaulters [1] and large defaulters [2]. Additionally, they must report **quarterly** for total exposure in specific cases involving credit risk transfer instruments [4]. Other reporting requirements, such as for structured digital lending products [5], are governed by extant rules but do not specify a frequency. Relief measures related to stressed assets are reported **half-yearly** [6].</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1595,11 +1544,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>An NBFC identified in the Upper Layer must list its equity shares within **three years** of identification [1], [2].  
-**Conditions and exceptions**:  
-- The provision does not apply to NBFC-ULs fully owned and controlled by the Government [1], [2].  
-- The timeline is triggered upon identification by the Reserve Bank [2].  
-- The requirement is separate from the 24-month transition period for adopting enhanced regulatory frameworks [3].</t>
+          <t>An NBFC identified in the Upper Layer must list its equity shares within **three years** of identification [1], [2]. However, this requirement **does not apply to NBFC-UL (Upper Layer) fully owned and controlled by the Government** [1], [2].</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1618,7 +1563,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1652,7 +1597,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No, collection staff cannot call borrowers late at night if the borrower is not picking up during the day. The guidelines explicitly prohibit contacting borrowers outside specific time frames. For instance, recovery agents must contact customers between **8:00 a.m. to 7:00 p.m.** for overdue loans [3](#3-6-e), and persistently calling before **8:00 a.m.** or after **7:00 p.m.** is deemed harassment [4](#4). Additionally, calling at "odd hours" is explicitly forbidden as part of undue harassment [4](#4). These rules apply regardless of whether the borrower answers during the day.</t>
+          <t>No, collection staff cannot call borrowers late at night if the borrower is not picking up during the day. The NBFC and HFC guidelines strictly prohibit contacting borrowers outside specific time frames. Recovery agents must contact customers between **8:00 a.m. to 7:00 p.m.** for recovery of overdue loans [3][6](e). Additionally, persistently calling before **8:00 a.m.** or after **7:00 p.m.** is explicitly deemed a harsh method and prohibited [1][2][4]. If the borrower is unavailable during the day, the NBFC/HFC must honor the borrower's request to avoid calls at specific times [3][6](f). Thus, late-night calls are not permitted under these regulations.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1671,7 +1616,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1705,7 +1650,10 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>If a borrower pays off the overdue interest but still owes some principal, the account **cannot** be taken out of NPA status. According to paragraph 24 of the context, loan accounts classified as NPAs may be upgraded as "standard" assets **only if entire arrears of interest and principal are paid** by the borrower. Since the principal remains unpaid, the account remains classified as NPA. Additionally, paragraph 25 specifies that for borrowers with multiple credit facilities, upgrades from NPA to standard assets require repayment of **all** arrears across all facilities. Thus, partial payments (e.g., only interest) do not satisfy the criteria for upgradation [2].</t>
+          <t>If a borrower pays off the overdue interest but still owes some principal, the account **cannot** be taken out of NPA status. According to the passages:  
+- **Paragraph 24** states that loan accounts classified as NPAs may be upgraded to "standard" only if **entire arrears of interest and principal** are paid by the borrower [2].  
+- **Paragraph 25** further clarifies that for borrowers with multiple credit facilities, upgrades from NPA to standard require repayment of **entire arrears** across all facilities [2].  
+Thus, partial payment of overdue interest without settling the principal does not suffice to remove the account from NPA classification.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1724,7 +1672,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1758,7 +1706,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>When rates go up, floating-rate borrowers are **not required** to switch to a fixed rate. The NBFC may, at its option, provide borrowers the choice to switch to a fixed rate as per its Board-approved policy [1]. This option is not mandatory, and borrowers can choose to either opt for enhanced EMI/elongated tenor or prepay without switching [1]. The decision to switch is discretionary for both the NBFC and the borrower.</t>
+          <t>When rates go up, floating-rate borrowers are **not required** to switch to a fixed rate. The NBFC may, at its option, provide borrowers with the choice to switch to a fixed rate during a reset of interest rates, as per the policy framework outlined in [1]. This option is not mandatory for borrowers, and the decision to switch depends on the NBFC's approved policy and the borrower's preference. The regulations emphasize transparency and borrower choice but do not compel switching [1].</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1777,7 +1725,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1811,7 +1759,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No, penal interest cannot be added when a customer pays late. Penal charges for non-compliance of material terms and conditions must be levied as separate charges, not as penal interest added to the interest rate [1]. Interest may only be charged on unpaid interest (including unpaid EMI) at the contracted rate until remediation, but not at the penal rate [1]. For credit cards, late payment charges are levied only on the outstanding amount after the due date, not on the total amount due [3][6]. Penal charges cannot be capitalized (i.e., further interest computed on them) [2]. Additionally, NBFCs must ensure transparency by disclosing penal charges upfront in loan agreements and billing statements [2][6].</t>
+          <t>No, penal interest cannot be added when a customer pays late. Penal charges for non-compliance of material terms and conditions must be levied as **penal charges**, not as **penal interest** [1]. Interest can only be charged on unpaid interest (including unpaid EMI) at the **contracted rate of interest** until remediation, but not at the penal rate [1]. Additionally, **capitalisation of penal charges** (i.e., interest on penal charges) is explicitly prohibited [2]. For credit cards, late payment charges are allowed but must be transparent and applied only to the outstanding amount after the due date, not the total amount due [3].</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1830,7 +1778,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1864,7 +1812,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>No, the classification of an NBFC as being in the Upper Layer is determined by the Reserve Bank of India (RBI) based on specific parameters and criteria, not by the entity itself. The RBI identifies NBFCs for inclusion in the Upper Layer under the Scale Based Regulation framework [2][3]. Additionally, once identified as NBFC-UL (Upper Layer), the entity must comply with enhanced regulatory requirements for at least five years, unless it meets specific conditions to exit the framework [4]. Government-owned NBFC-ULs are exempt from certain provisions [1]. The RBI also oversees the transition process, including timelines and implementation plans [6]. Thus, the decision to categorize an NBFC in the Upper Layer is exclusively made by the RBI.</t>
+          <t>No, the classification of an NBFC into the Upper Layer is not self-declared. The Reserve Bank of India (RBI) determines this based on predefined parameters under the scale-based regulatory framework [2][3]. Once identified as NBFC-UL (Upper Layer), the entity must comply with enhanced regulatory requirements, including listing within three years [1], and cannot unilaterally decide their layer status. The transition to the Upper Layer involves RBI-advisory timelines and Board-approved implementation plans [6]. Additionally, government-owned NBFC-ULs are exempt from certain provisions [1].</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1883,7 +1831,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1917,7 +1865,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>No, the NBFC cannot charge a foreclosure fee for prepaying a floating-rate personal loan. According to [3] paragraph 34(1), pre-payment charges are explicitly prohibited for floating rate loans granted for purposes other than business to individuals. This includes personal loans, as the customer's loan is for personal use (salaried individual). Additionally, [3] (7) clarifies that no charges can be levied if prepayment is initiated by the borrower, which applies here. Exceptions or additional conditions in [3] (5) and (9) do not override this rule for personal loans.</t>
+          <t>No, the NBFC cannot charge a foreclosure fee for prepaying a floating-rate personal loan (non-business purpose) as per the provisions. 
+**Conditions and exceptions:**  
+1. **Floating rate loans for non-business purposes to individuals** (like personal loans) are explicitly exempt from pre-payment charges under **paragraph 34(1)** of the Directions [3].  
+2. **Pre-payment charges are prohibited** if the loan is on a floating rate at the time of prepayment, as clarified in **paragraph 34(4)** [3].  
+3. **No retrospective charges** can be levied if prepayment is initiated by the borrower, as per **paragraph 34(9)** [3].  
+4. **Disclosure requirements** mandate that pre-payment charges (if any) must be explicitly stated in the sanction letter and Key Facts Statement (KFS), but since the loan is floating-rate and non-business, no such charges apply [3].  
+Thus, the NBFC must **not levy foreclosure fees** for early prepayment of this type of loan.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1890,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1970,11 +1924,10 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>The lending app partner **cannot** collect EMIs into its own bank account and forward them to you, as per the regulations. According to passage [3], funds from borrowers must be transferred through escrow accounts operated by a bank trustee. Specifically:  
-- Repayment amounts must first go to the **Borrowers' Escrow Account**, which then transfers funds to the respective lender's bank account [3].  
-- Cash transactions are strictly prohibited, and all transfers must occur through bank accounts [3].  
-- Funds from the **Lenders' Escrow Account** (for disbursal) or **Borrowers' Escrow Account** (for repayment) cannot be used for disbursement or repayment outside the escrow mechanism [3].  
-Thus, the app partner must route EMIs through the escrow process, not directly into its own account. If the app partner is the lender, it would receive EMIs via the escrow mechanism, not directly. If it is an intermediary (e.g., LSP), it cannot hold or forward EMIs into its own account.</t>
+          <t>The lending app partner **cannot** collect EMIs into its own bank account and forward them to you. According to the context passages:  
+- **Passage [3]** mandates that funds from lenders must go into the "Lenders' Escrow Account" and can only be disbursed to the borrower's bank account after compliance checks. Similarly, borrower repayments must go into the "Borrowers' Escrow Account" and then transferred to lenders' accounts. Direct collection into a third-party account (like the app partner's) is prohibited [3].  
+- **Passage [4]** explicitly states that loan disbursements must be made into the borrower's bank account, and repayments must flow directly from the borrower's account to the NBFC, with LSPs (like the app partner) having no control over fund flows [4].  
+Thus, collecting EMIs into the app partner's account violates the prescribed funds transfer mechanisms and is not permitted.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1946,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>10.7</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2027,12 +1980,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>The customer has **30 days** from the date of filing the complaint with the NBFC to resolve the grievance. If the NBFC does not respond within this period, rejects the complaint wholly/partly, or the customer is unsatisfied with the resolution, they can approach the RBI Ombudsman [1][3][6]. 
+          <t>The customer has **30 days** from the date of filing the complaint with the card-issuer/NBFC to resolve the grievance. If the card-issuer does not respond within this period, rejects the complaint wholly/partly, or the customer is unsatisfied with the resolution, they can approach the RBI Ombudsman [1][3][6]. 
 **Conditions and exceptions**:  
 - The 30-day period starts from the date the NBFC receives the complaint [1][3][6].  
-- If the complaint is partially resolved or wholly rejected, the customer must escalate to the RBI Ombudsman within this timeframe [3][6].  
-- The RBI Ombudsman is also the redressal option if the NBFC’s grievance redressal mechanism fails to resolve the complaint within 30 days [1][3][6].  
-- The 30-day limit applies to all complaints under the Reserve Bank-Integrated Ombudsman Scheme, 2021, except those excluded under specific clauses (e.g., disputes under Section 18 of CICRA, 2005) [4].</t>
+- If the complaint is partially resolved or wholly rejected by the NBFC, the customer may also approach the RBI Ombudsman [3][6].  
+- The RBI Ombudsman is the designated authority for NBFCs covered under the Reserve Bank - Integrated Ombudsman Scheme, 2021 [3][6].  
+- For NBFCs not covered under this scheme, the Consumer Education and Protection Cell (CEPC) of the RBI's Regional Office is the alternative [3][4].  
+- The NBFC must provide a complaint number/docket number for tracking, even if the complaint is received via phone [1].  
+- The RBI Ombudsman's portal (https://cms.rbi.org.in) and physical address are provided for filing complaints [1][3][6].</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2051,7 +2006,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2085,7 +2040,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No, the entire internal audit function cannot be outsourced to an outside firm. The NBFC shall not outsource the Internal Audit function [1], and core management functions including internal audit are explicitly listed as non-outsourcable [3]. While external experts may be hired on a contractual basis for specific tasks (e.g., IT/IS audit) if internal expertise is lacking, ownership of audit reports must always remain with the internal audit function's regular functionaries [1]. Additionally, outsourcing internal audit would conflict with the requirement that internal auditors act independently of management [4].</t>
+          <t>No, the entire internal audit function cannot be outsourced. The NBFC shall not outsource the Internal Audit function [1], and core management functions like internal audit are explicitly listed as non-outsourcable [3]. While experts or external agencies may be hired for specific tasks (e.g., IT/IS audit) under certain conditions [4], the ownership of audit reports must always remain with the internal audit function's regular personnel [1]. Outsourcing the entire function is prohibited even within a group or conglomerate, except under strict compliance with specific regulatory instructions [3].</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2104,7 +2059,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2138,7 +2093,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>The NBFC is required to appoint a Chief Compliance Officer (CCO) to head the Compliance Department, as per [1] and [5], but there is no provision for rotating the CCO annually. The passages specify that the CCO must ensure independence and resourcing of the Compliance function [1], but they do not mention rotation timelines for the CCO role. Audit firm rotation rules (e.g., every three years for auditors [2][3]) apply to statutory auditors, not compliance heads. Thus, rotating the CCO every year is not mandated or prohibited by the provided contexts.</t>
+          <t>The passages do not explicitly require a separate compliance head, but they mandate the appointment of a Chief Compliance Officer (CCO) to head the Compliance Department [1], [4]. There is no mention of rotating compliance heads annually. However, the passages do specify rotation rules for **statutory auditors**, not compliance officers: audit firms cannot be reappointed in the same NBFC for six years after completing a term [3]. Compliance officers are not subject to annual rotation as per the provided texts.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2148,16 +2103,16 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>no numeric facts to compare - read the answer yourself</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2191,13 +2146,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yes, loan terms must be explained in a language the borrower understands.  
-- The Key Facts Statement (KFS) must be written in a language understood by the borrower [1].  
-- The NBFC must convey loan terms in the vernacular language or a language as understood by the borrower, including penalties for late repayment [2].  
-- The loan agreement and standard form for microfinance loans must be in a language understood by the borrower [3].  
-- Notices about changes in terms and conditions must be in the vernacular or a language the borrower understands [4].  
-- All communications to the borrower, including terms and conditions, must be in the regional language or a language chosen by the borrower [5].  
-- For illiterate borrowers, important terms must be explained in the presence of a witness (not an NBFC employee) [6].</t>
+          <t>Yes, loan terms must be explained in a language the borrower understands. This is explicitly required across multiple passages:  
+- The Key Facts Statement (KFS) must be written in a language understood by borrowers [1].  
+- Terms and conditions must be conveyed in the vernacular language or a language as understood by the borrower, with penalties for late repayment highlighted in bold [2].  
+- Loan agreements and standard forms must be in a language understood by the borrower [3].  
+- Notices about changes in terms, disbursement schedules, or interest rates must be in the borrower’s understandable language [4].  
+- All communications, including terms and conditions, must be in the regional language or the borrower’s chosen language, with illiterate borrowers’ terms explained by a witness [5].  
+- Communications affecting the borrower’s interests must be in the regional language or the borrower’s chosen language [6].  
+Exceptions: Credit card receivables are exempt from some KFS requirements [1], but this does not apply to general loan terms.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2216,7 +2172,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2250,11 +2206,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yes, before selling a repossessed vehicle, the borrower must be warned. The terms and conditions of the loan agreement must include a notice period before taking possession of the security [1][4], and the borrower must be given a final chance to repay the loan before the sale/auction of the property [1][3]. These provisions ensure transparency and legal compliance. 
-**Conditions and exceptions**:  
-- The notice period and final repayment opportunity are mandatory unless waived under specific circumstances [3].  
-- The procedure for repossession and sale/auction must strictly follow the disclosed recovery policy and legal frameworks like the SARFAESI Act [4].  
-- The borrower must be informed of these terms at the time of contract execution [1][4].</t>
+          <t>Yes, before selling a repossessed vehicle, the borrower must be given a final chance to repay the loan. This is explicitly required under the terms and conditions of the loan agreement, which must include a provision regarding the borrower's final opportunity for repayment before the sale/auction of the property [1][3]. Additionally, the notice period before taking possession and the procedure for sale/auction of the property are mandated as part of the legally enforceable re-possession clause [1][3]. These steps ensure transparency and compliance with the responsible business conduct guidelines.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2273,7 +2225,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2307,11 +2259,10 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A depositor cannot get their money back two months after investing unless specific exceptions apply. Premature repayment is generally not allowed within three months from the deposit date, as per paragraph 35 of the NBFC regulations [1]. However, exceptions exist:  
-- **Tiny deposits** may be fully repaid without interest before three months, but "tiny deposits" is not quantified in the passage [3].  
-- **Critical illness** allows 100% repayment without interest before three months, but this requires explicit documentation of the critical illness [3].  
-- Other deposits may have partial repayment (up to 50% or ₹5 lakh) for emergent expenses, but this also depends on specific conditions [3].  
-Without meeting these exceptions, repayment within three months is prohibited.</t>
+          <t>The depositor cannot get their money back two months after investing unless specific exceptions apply. Premature repayment of public deposits by an NBFC is generally not allowed within three months from the date of deposit [1]. However, exceptions exist:  
+- **Tiny deposits** may be fully repaid without interest before three months, but "tiny deposits" are not quantified in the passage [3].  
+- **Critical illness** allows 100% repayment without interest before three months [3].  
+Since the depositor’s request is for two months (before the three-month threshold) and no exception (like critical illness or tiny deposits) is specified, the NBFC is not obligated to repay prematurely.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2321,16 +2272,16 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>found 50%, 5lakh; missing 10000</t>
+          <t>none of the expected figures appear (10000, 50%, 5lakh)</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2364,7 +2315,13 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yes, different interest rates can be charged to borrowers who seem similar, but with specific conditions. The NBFC must base the rates on relevant factors like cost of funds, margin, and risk premium, and disclose the rationale for different rates to different borrower categories [1]. Penal charges within the same product category may vary based on loan amount but must remain reasonable, non-discriminatory, and aligned with the borrower's risk profile [3]. Additionally, for credit cards, differential interest rates based on payment/default history are allowed if transparent and auditable [5]. However, penal charges for individual borrowers must not exceed those for non-individuals in similar non-compliance cases [3]. All variations must be explicitly communicated to borrowers in loan agreements, sanction letters, and disclosed on the NBFC's website [1][3].</t>
+          <t>Yes, different interest rates can be charged to borrowers who seem similar, provided certain conditions are met. The passages specify that:  
+1. **Risk-based differentiation** is allowed, as NBFCs must adopt interest rate models considering factors like cost of funds, margin, and risk premium, with rates disclosed to borrowers [1].  
+2. **Blended rates** are permitted under CLA, where rates are weighted by the proportionate funding share of REs based on the borrower’s risk profile [2].  
+3. **Penal charges** may vary within the same product category depending on loan amount, but must be reasonable, non-discriminatory, and not exceed those for non-individual borrowers for similar non-compliance [3].  
+4. **Transparency** is mandatory: rates and rationale must be disclosed in loan agreements, sanction letters, and on websites [1][2][3].  
+5. **No arbitrary discrimination**: For example, penal charges for individual borrowers cannot exceed those for non-individuals for similar defaults [3].  
+However, rates must be **annualized**, **updated promptly**, and **communicated explicitly** to borrowers [1][24]. Differentiation must not involve credit enhancement or default guarantees [111].</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2383,7 +2340,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>10.1</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2417,12 +2374,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yes, there is a cap: the repayment obligations of a microfinance borrower cannot exceed **50 per cent of the monthly household income** [1].  
-**Conditions and exceptions**:  
-1. **Future income exclusion**: Income from assets financed by the loan is excluded from household income calculations [1].  
-2. **Existing loans**: Loans where repayment obligations exceed 50% of income are allowed to mature but cannot receive new loans until compliance is achieved [1].  
-3. **Compliance monitoring**: NBFCs must ensure adherence via borrower declarations, bank statements, and local enquiries [1].  
-4. **Collateral-free nature**: Microfinance loans are explicitly collateral-free and not linked to deposit accounts or security hypothecation [3].</t>
+          <t>Yes, there is a cap: the outflows on account of repayment of monthly loan obligations of a household shall not exceed **50 per cent of the monthly household income** [1]. This limit applies to all outstanding loans (collateral-free microfinance loans and other collateralized loans) of the household [1]. Additionally, **future expected income from the asset/activity financed by the loan is excluded** from the calculation of household income for indebtedness purposes [1].</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2441,7 +2393,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2475,12 +2427,13 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>The provisions of Chapter III (outsourcing arrangements) apply to your Middle Layer NBFC launching app-based personal loans through a service provider, as these directions cover material outsourcing arrangements with service providers (related or unrelated) for financial services like loan processing [1]. Additionally, Chapter IV and IT-specific provisions in Chapter II apply to Middle Layer NBFCs [1]. For prudential norms, your NBFC (as NBFC-D, ICC, Factor, IFC, MFI, HFC, CIC, or IDF-NBFC) falls under the scope of the prudential norms in passage [5], subject to layer-wise applicability. However, the following exceptions apply:  
-- **Credit card-specific provisions** in Chapter III are excluded unless explicitly related to credit cards [1].  
-- **NBFC-P2P, NBFC-AA, NOFHC, and Type I NBFCs** are excluded from most directions, but your NBFC is not categorized as such [1][4][5].  
-- **MGCs and SPDs** are excluded, but your service provider is not explicitly mentioned as such [1][4].  
-- **Base Layer NBFCs with customer interface but no public funds** are excluded, but your NBFC is in Middle Layer [4][6].  
-Ensure compliance with outsourcing policies, IT governance, and prudential norms for your layer.</t>
+          <t>The provisions of Chapter III of the Directions apply to your Middle Layer NBFC's app-based personal loans through a lending service provider, as these are material outsourcing arrangements for financial services like loan processing [1]. Additionally, IT-specific provisions in Chapter II (e.g., Board-level IT outsourcing policy) apply to NBFCs in Middle Layer and above [1]. For outsourced services, ensure compliance with the Reserve Bank of India (Non-Banking Financial Companies - Credit Cards: Issuance and Conduct) Directions, 2025, if credit card-related, though this may not apply to personal loans [1]. 
+**Conditions and exceptions:**  
+- **Exclusions:** These Directions do not apply to NBFC-P2P, NBFC-AA, NOFHC, or Type I NBFCs [1][4][5].  
+- **Layer-specific applicability:** For Middle Layer NBFCs, paragraphs 6–19, 23–33, and 50–52 of the Directions apply [2].  
+- **IT requirements:** Chapter IV and IT-specific Chapter II provisions (e.g., Board reviews) are mandatory for Middle Layer and above [1].  
+- **Service provider scope:** The provisions cover outsourcing to both group members and unrelated parties, including app-based lending [1].  
+Ensure compliance with all layer-specific and outsourcing-related provisions in the Directions.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2499,7 +2452,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2533,7 +2486,13 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Once your NBFC crosses ₹1,000 crore in asset size, it will transition to the Middle Layer (NBFC-ML) and be subject to regulatory requirements under paragraph 34 of the Directions [1]. This includes stricter audit criteria: for asset sizes above ₹1,000 crore, you must appoint audit firms with a minimum of 5 full-time partners (FTPs), 4 FCA partners, 2 CISA/ISA-qualified professionals, 15 years of audit experience, 18 professional staff, and exclusive association of partners as defined [6]. Additionally, stress reporting rules for Middle Layer NBFCs (e.g., provisioning rates for sub-standard assets) will apply instead of Base Layer rules [4]. Even if your asset size temporarily falls below ₹1,000 crore due to fluctuations, you must continue complying with Middle Layer requirements until your next audited balance sheet is submitted to the RBI [1]. Note that group consolidation does not apply here, as you are a standalone NBFC [2].</t>
+          <t>Once your NBFC's asset size crosses ₹1,000 crore, you will transition from Base Layer (NBFC-BL) to Middle Layer (NBFC-ML) status, triggering the following changes:  
+1. **Regulatory Compliance**: You will be subject to the regulatory requirements outlined in paragraph 34 of the Directions [1], including stricter reporting and operational norms applicable to NBFC-ML.  
+2. **Audit Requirements**: Your audit firm must meet enhanced criteria for NBFCs above ₹1,000 crore, such as a minimum of 3 full-time partners (FTPs), 2 FCA partners, 1 CISA/ISA-qualified CA, 8 years of audit experience, and 12 professional staff [6].  
+3. **Classification**: References to your entity will shift from NBFC-ND (Base Layer) to NBFC-ML (Middle Layer) as per updated terminology effective October 1, 2022 [3].  
+4. **Consolidation (if applicable)**: If part of a group, consolidated assets of the group will determine ML status, but since you are standalone, this does not apply [2].  
+5. **Temporary Fluctuations**: If your asset size temporarily falls below ₹1,000 crore due to market dynamics, you must still comply with ML regulations until the next audited balance sheet submission [1].  
+These changes apply regardless of when you cross the ₹1,000 crore threshold.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2552,7 +2511,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>12.3</v>
+        <v>13.9</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2586,17 +2545,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yes, a non-deposit-taking Middle Layer NBFC can start accepting public deposits, but it must comply with specific conditions. 
-**Conditions and Limitations:**  
-1. **Classification as Deposit-Taking NBFC**: The NBFC must be classified as a deposit-taking NBFC under the Scale-Based Regulation (SBR) framework. Middle Layer NBFCs are generally subject to the Acceptance of Public Deposits Directions unless exempt [5].  
-2. **Net Owned Funds (NOF) Threshold**: The NBFC must meet the minimum NOF requirement stipulated by the Reserve Bank [4].  
-3. **Prudential Norms**: It must comply with all prudential norms, including limits on deposit acceptance (up to 1.5 times its NOF) and restrictions on renewing matured deposits without depositor consent [4].  
-4. **Resolutions**: If the NBFC previously fell under the exemption for non-deposit-taking NBFCs, it must pass resolutions confirming it will accept public deposits and adhere to regulatory requirements [3].  
-5. **Application Form Compliance**: It must use standardized application forms for public deposits, including disclosures about credit ratings, dispute resolution mechanisms, and financial transparency [6].  
-**Exceptions**:  
-- NBFCs not accepting public deposits (e.g., Type I NBFCs) are exempt from these rules but cannot transition to deposit-taking without meeting the above criteria [1][3].  
-- The Reserve Bank may grant exemptions or extensions for compliance with specific provisions if necessary [3].  
-**Key Citations**: [1][3][4][5][6]</t>
+          <t>We are a non-deposit-taking Middle Layer NBFC and cannot start accepting public deposits unless we meet specific criteria. The passages do not explicitly permit transitioning from non-deposit-taking to deposit-taking status. However, if we do accept public deposits, we must comply with the following:  
+1. **NOF Limit**: Public deposits accepted/renewed cannot exceed 1.5 times our Net Owned Funds (NOF) [4].  
+2. **Prudential Norms**: We must comply with all prudential norms [4].  
+3. **Classification**: As a Middle Layer NBFC under the Scale Based Regulation (SBR) framework, accepting deposits would reclassify us as a deposit-taking NBFC, subject to stricter regulations [5].  
+4. **Board Resolutions**: If we start accepting deposits, we must cease being exempt under [3](iii) and adhere to the applicability of the "Acceptance of Public Deposits" Directions [3].  
+The passages do not directly authorize this transition, so further clarification from the RBI may be required.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2615,7 +2569,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>13.2</v>
+        <v>16.2</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2649,7 +2603,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The applicable LTV ratio for gold loans is determined by the NBFC's credit policy as per paragraph 32 of the Reserve Bank of India (Non-Banking Financial Companies - Credit Facilities) Directions, 2025, which requires specifying the maximum permissible LTV ratio for loans against eligible collateral (including gold or silver). However, the exact LTV percentage is not explicitly stated in the provided passages [1]. The context only mentions a 50% LTV ratio for loans against **listed shares** (passage [2]), which is distinct from gold loans. Thus, the NBFC must define its own LTV ratio in its policy, subject to regulatory guidelines.</t>
+          <t>The LTV ratio applicable for gold loans is determined by the NBFC's credit policy as per the Reserve Bank of India (Non-Banking Financial Companies - Credit Facilities) Directions, 2025, as amended [4]. However, the specific percentage is not explicitly stated in the provided passages. The policy must include the "maximum LTV ratio permissible for such loans" [1], but the exact figure depends on the NBFC's internal guidelines aligned with regulatory requirements. For loans against gold or silver collateral, the LTV ratio is not directly specified here, and the NBFC must define it in its policy.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2668,7 +2622,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2702,24 +2656,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>You must ensure the following:  
-1. **Written Agreements**: Define terms and conditions in legally binding agreements, vetted by legal counsel, and include risk mitigation strategies [1].  
-2. **Access to Records**: Ensure NBFC access to all books, records, and information relevant to the outsourced activity, including audit trails and logs for technology-related tasks [1][3].  
-3. **Monitoring &amp; Oversight**: Conduct continuous monitoring of the service provider to enable immediate corrective actions and ensure adequate systems for data protection [1][3].  
-4. **Confidentiality &amp; Liability**: Include controls for data confidentiality, service provider liability for breaches, and post-termination safeguards for customer information [1][3].  
-5. **Contingency Plans**: Have business continuity plans and testing requirements to ensure uninterrupted operations [1][3].  
-6. **Audit Rights**: Allow NBFC and RBI to audit the service provider, access documents, and inspect its books and accounts [1][3].  
-7. **Termination Clauses**: Include a termination clause with a minimum notice period and provisions for post-termination data preservation [1][3].  
-8. **Subcontractor Management**: Require subcontractors to meet service standards and grant NBFC audit rights over them [3].  
-9. **Legal Compliance**: Ensure compliance with the Information Technology Act, 2000, and other legal standards to protect customer data [3].  
-10. **Data Storage**: Store data only in India if required by regulations [3].  
-11. **Service Level Agreements (SLAs)**: Define performance criteria and deliverables to measure service quality [3].  
-12. **Non-Disclosure Agreements**: Mandate NDAs for information retained by the service provider [3].  
-13. **Board Oversight**: Ensure the Board oversees outsourcing operations and risk management, with Senior Management accountable for decisions [2][6].  
-14. **Cyber Incident Reporting**: Report cyber incidents to RBI within six hours of detection by the service provider [6].  
-15. **Ownership Restrictions**: The service provider (if not a group company) must not be owned or controlled by NBFC directors, key personnel, or their relatives, unless approved by the Board with disclosure [4][6].  
-16. **Prohibited Impediments**: Ensure outsourcing does not hinder RBI’s supervisory functions or the NBFC’s ability to fulfill regulatory obligations [4].  
-Exceptions: If the service provider is owned by NBFC directors/relatives, board approval with oversight is allowed [6].</t>
+          <t>As a Middle Layer NBFC outsourcing collections, you must ensure the following:  
+1. **Written Agreement**: Define terms and conditions in a legally binding agreement, vetted by legal counsel, and include provisions for service standards, access to books/records, continuous monitoring, subcontractor approval, confidentiality controls, contingency plans, audit rights, RBI access, termination clauses, and post-termination confidentiality [1][3].  
+2. **IT-Specific Requirements**: For IT services, ensure alignment with strategic plans, data protection systems, and compliance with the Information Technology Act, 2000. Include SLAs, data storage in India, data sharing permissions, and subcontractor liability clauses [2][3].  
+3. **Offshore Compliance**: If outsourcing offshore, ensure the jurisdiction upholds confidentiality, specify governing law, maintain record accessibility, prevent interference with RBI supervision, and store original records in India [5].  
+4. **Governance &amp; Oversight**: Ensure the service provider is not owned by NBFC directors/relatives (unless approved by the Board). Conduct comprehensive risk assessments, monitor cyber incidents (reporting within 6 hours of detection), and maintain governance mechanisms [4][6].  
+5. **Audit &amp; Inspection Rights**: Allow RBI or authorized persons to inspect the service provider, access NBFC’s IT infrastructure, and review audit trails/logs [1][2][5].  
+6. **Data Security**: Implement controls for confidentiality, including NDAs, and ensure subcontractors comply with RBI directions and data protection standards [3][4].  
+7. **Business Continuity**: Adopt RBI-approved business continuity practices and ensure the service provider maintains readiness for disruptions [2][6].</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2738,7 +2682,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2772,7 +2716,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yes, as a Middle Layer NBFC, you are required to implement a robust IT strategy with a capacity management plan to meet evolving demand and periodically review your IT/IT security architecture and technology platform [1] §19. Additionally, you must adhere to baseline cybersecurity requirements, including physical/logical access controls, password policies, user roles, and backup systems with periodic testing [2] §8. Your EWS framework must integrate with Core Banking Solutions (CBS) or other operational systems for fraud risk monitoring [4] §17(1). These requirements apply regardless of the number of branches.</t>
+          <t>Yes, as a Middle Layer NBFC, you have core technology system requirements. These include:  
+1. **Integration with Core Banking Solution (CBS)**: The Early Warning Signals (EWS) framework must be integrated with CBS or other operational systems [4].  
+2. **Board-approved IT/IS Policy**: Your IT systems must include physical/logical access controls, password policies, user roles, maker-checker concepts, and robust cybersecurity controls [2].  
+3. **Business Continuity Plan (BCP)**: A BCP policy must be approved by the Board, with periodic reports (at least annually) [2].  
+4. **Data Backup and Testing**: Arrangements for data backup with periodic testing are mandatory [2].  
+5. **Risk Assessment and Technology Stack**: Your risk assessments must evaluate the technology stack, known vulnerabilities, and remedial actions [1].  
+6. **Periodic Testing of Systems**: Backed-up data and applications must be tested at least half-yearly to ensure recovery without transaction loss or audit-trail disruption [1].  
+These requirements ensure resilience, security, and compliance with regulatory standards.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2742,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2825,7 +2776,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>No, a Middle Layer NBFC cannot charge prepayment fees on floating-rate term loans sanctioned for business purposes to micro and small enterprises (MSEs) with a sanctioned amount/limit up to ₹50 lakh [1][34(2)(ii)]. For loans exceeding ₹50 lakh, prepayment fees may be levied, but only if explicitly disclosed in the sanction letter and Key Facts Statement (KFS), and without retrospective application [1][34(8)(9)]. Additionally, prepayment charges must not apply if the borrower notifies the NBFC of non-renewal intent before the due date for cash credit/overdraft facilities [1][34(6)].</t>
+          <t>No, a Middle Layer NBFC cannot charge pre-payment charges on floating-rate term loans sanctioned for business purposes to micro and small enterprises (MSEs) if the sanctioned amount/limit is up to ₹50 lakh [1][34(2)(ii)]. For loans exceeding ₹50 lakh, the passages do not explicitly prohibit pre-payment charges, but the NBFC must ensure compliance with other applicable regulations. Additionally, pre-payment charges must be disclosed in the sanction letter and loan agreement, and no retrospective charges are allowed [1][34(8)].</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2844,7 +2795,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>11.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2878,14 +2829,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The main new obligations for an identified Upper Layer NBFC are:  
-1. **Mandatory listing within three years** of identification, with a Board-approved roadmap for compliance with listed company disclosure requirements under SEBI's 2015 Regulations [1][3].  
-2. **Implement enhanced regulatory framework** within 24 months from classification, including calibrated business increment allowances during transition [2].  
-3. **Submit the implementation roadmap** to the Reserve Bank for supervisory review [2].  
-4. **Ensure Board composition** with competent members having relevant educational qualifications and experience [3].  
-5. **Subject to enhanced regulatory requirements for at least five years**, even if criteria are not met in subsequent years, unless exiting via voluntary strategic adjustments (not due to adverse financial conditions) [4].  
-6. **Government-owned NBFC-ULs are exempt** from some provisions [1][3].  
-These obligations apply unless the NBFC is fully government-owned.</t>
+          <t>The main new obligations for an NBFC identified as Upper Layer (UL) are:  
+1. **Mandatory listing within three years** of identification, with a Board-approved roadmap for compliance with listed company disclosure requirements under the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 [1][3].  
+2. **Implementation plan**: Within three months of classification, the NBFC must adopt a Board-approved policy for the enhanced regulatory framework and outline an implementation plan, which must be submitted to the Reserve Bank for supervisory review [2].  
+3. **Compliance timeline**: The Board must ensure adherence to UL stipulations within **24 months** from the date of Reserve Bank classification, with transitional flexibility for calibrated business adjustments [2].  
+4. **Enhanced regulatory period**: The NBFC remains subject to heightened regulatory requirements for **at least five years** post-classification, unless it meets criteria to exit the framework after five consecutive years of non-compliance [4].  
+5. **Disclosure requirements**: Even before listing, the NBFC must implement disclosure standards equivalent to those of a listed company [3].  
+6. **Government-owned exemptions**: Provisions do not apply to NBFC-ULs fully owned and controlled by the Government [1][3].  
+These obligations apply unless the NBFC voluntarily adjusts operations (not due to adverse financial conditions) to exit the enhanced framework earlier [4].</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2904,7 +2855,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2938,12 +2889,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The applicable risk weight for unsecured consumer loans (categorized as retail loans excluding housing loans, educational loans, vehicle loans, loans against gold jewellery, and microfinance/SHG loans) is **125%** [2].  
-**Conditions and exceptions:**  
-- This applies to exposures not covered under zero-risk-weight schemes (e.g., CGTMSE, CRGFTLIH, NCGTC guarantees) [2(iv)].  
-- If the loans are guaranteed under the Emergency Credit Line Guarantee Scheme (ECLGS) 5.0, **75% of the guaranteed portion** attracts **0% risk weight** (for settlement within 30 days), while the remaining 25% retains the 125% risk weight [4].  
-- Exposures to the Government of India/State Governments (with zero risk weight) or fully government-guaranteed claims (20% risk weight) are exempt [1(13), 2(iii)].  
-- Loans to NBFC subsidiaries or group companies (reduced from Owned Funds) are exempt from exposure norms but still subject to risk weights per their classification [1(17)].</t>
+          <t>The risk weight for unsecured consumer loans (excluding housing, educational, vehicle, gold jewellery, and microfinance/SHG loans) is **125%** as per the Risk Weight Assets (RWAs) guidelines [3]. 
+**Conditions and exceptions**:  
+- If the loans are fully guaranteed by the Government of India, the risk weight is **0%** [1].  
+- If the loans are guaranteed under schemes like CGTMSE, CRGFTLIH, or NCGTC (with conditions met), the risk weight could be **0%** for eligible portions [2].  
+- For exposures under the Emergency Credit Line Guarantee Scheme (ECLGS) 5.0, **75% of the guaranteed portion** attracts **0% risk weight** (if settlement is expected within 30 days), while the remaining exposure follows standard risk weights [4].  
+Since the question does not specify guarantees or schemes, the default risk weight for unsecured consumer loans is **125%**.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2953,16 +2904,16 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>found 125%; missing 2023, 100%, 2025.</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>10.1</v>
+        <v>12.5</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2997,14 +2948,11 @@
       <c r="F46" t="inlineStr">
         <is>
           <t>The ₹6 crore loan to a director's relative falls under the following rules:  
-1. **Related Party Definition**: The relative is considered a "related party" under sub-clause (vb) of [5], as they are a relative of a director [5].  
-2. **Materiality Threshold**: For Middle Layer NBFCs, the materiality threshold is ₹5 crore [3]. Since the loan exceeds this threshold, it must be sanctioned by the NBFC's Board [3]. The NBFC may delegate this authority to a Committee of the Board (excluding the Audit Committee) [3].  
-3. **Applicability**: The NBFC is in the Middle Layer, so the materiality threshold of ₹5 crore applies [3].  
-4. **Exemptions**: No exemptions apply here, as the loan exceeds the threshold and the relative is a related party [5].  
-**Conditions**:  
-- The loan must comply with related party lending rules, including disclosure and approval processes.  
-- The NBFC must ensure the loan does not violate concentration risk limits or other prudential norms [2].  
-- The relative must not be a Government-owned entity, as such entities are excluded from being related parties under [5].</t>
+1. **Materiality Threshold**: For a Middle Layer NBFC, the materiality threshold is ₹5 crore [3]. Since the loan exceeds this threshold, it must be sanctioned by the NBFC's Board [3].  
+2. **Related Party Definition**: The relative of a director is classified as a "related party" under the NBFC's definitions, as per the Companies Act, 2013 [5(va)(i)(a)].  
+3. **Board Approval Requirement**: Loans to related parties exceeding the materiality threshold (₹5 crore) must be approved by the Board, with no delegation to the Audit Committee [3].  
+4. **Exemptions**: No exemptions apply here, as the loan amount exceeds the Middle Layer threshold.  
+These rules apply because the NBFC is in the Middle Layer, and the relative of a director is a related party.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3023,7 +2971,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -3057,16 +3005,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The key rules for your Middle Layer NBFC entering co-lending with a bank are:  
-1. **Co-lending governance**: Co-lending arrangements must comply with RBI Directions, 2025, ensuring no third party (other than lenders) has direct or indirect control over fund flows [1].  
-2. **Loan disbursement**: Loans must be disbursed directly into the borrower’s bank account, except for statutory mandates or specific end-use cases. Third-party accounts (including LSPs) are prohibited unless under "Digital Lending" provisions [1].  
-3. **Retention requirement**: Under CLAs, NBFCs must retain at least 10% of individual loans in their books [3].  
-4. **Internal policies**: Credit policies must include CLA-specific provisions, such as internal lending portfolio limits, borrower segmentation, due diligence of partners, and grievance redressal mechanisms [3].  
-5. **Disclosure**: Loan agreements must disclose role segregation (e.g., sourcing vs. servicing) and identify the single customer interface. Changes to this must be pre-notified to borrowers [3].  
-6. **Applicability**: These rules apply to NBFC-ML (Middle Layer) and above, including HFCs, and extend to all RBI-regulated entities, even if not classified as "lenders" under these Directions [5].  
-**Exceptions/Conditions**:  
-- For advances against salary, disbursal to the borrower’s account is allowed if repayment is directly from the employer’s account, with LSPs having no control over fund flows [1].  
-- Co-lending must adhere to RBI’s Transfer and Distribution of Credit Risk Directions, 2025, with strict fund control safeguards [1].</t>
+          <t>The key rules for a Middle Layer NBFC (NBFC-ML) entering co-lending with a bank are as follows:  
+1. **Co-lending Governance**: Co-lending arrangements must comply with the **Reserve Bank of India (Non-Banking Financial Companies - Transfer and Distribution of Credit Risk) Directions, 2025** [1]. No third party (including the bank) other than the lenders in the co-lending transaction shall have direct or indirect control over the flow of funds [1].  
+2. **Loan Retention**: NBFCs under a co-lending arrangement (CLA) must retain a **minimum 10% share** of individual loans in their books [3].  
+3. **CLA Agreement Requirements**: The CLA agreement must include:  
+   - Detailed terms and conditions of the arrangement [3].  
+   - Criteria for borrower selection, specific product lines, and fees for lending services [3].  
+   - Segregation of responsibilities between partners, timeframes for information exchange, and customer protection/grievance redressal mechanisms [3].  
+4. **Disclosure in Loan Contracts**: The loan agreement must disclose the roles and responsibilities of Recovery Entities (REs), including clear identification of the single point of contact with the borrower. Any change in customer interface requires prior intimation to the borrower [3].  
+5. **Eligibility Criteria**: The NBFC-ML must meet the following to participate in co-lending:  
+   - Owned fund of **₹500 crore or more** [2].  
+   - Capital Adequacy Ratio (CRAR) of **at least 15%** [2].  
+   - Net Non-Performing Assets (NPA) not exceeding **5% of total outstanding leased/hire purchase assets and advances** [2].  
+   - Net profit in the **preceding three consecutive financial years** [2].  
+6. **Compliance with Regulatory Framework**: The NBFC-ML must adhere to all applicable regulations for NBFC-ML, including reporting requirements, and ensure that co-lending does not violate scale-based regulatory frameworks [4][5].  
+These rules ensure compliance with RBI guidelines on co-lending, fund control, and borrower protections.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3085,7 +3038,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>8.9</v>
+        <v>14.1</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -3119,19 +3072,18 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The conditions for a Middle Layer NBFC onboarding customers via video KYC (V-CIP) include:  
-1. **Matching Identification Details**: The NBFC must ensure the customer’s photograph in Aadhaar/OVD matches the one during V-CIP, and the PAN/e-PAN details align with the customer’s provided information [2] (27.xiii).  
-2. **Concurrent Audit**: Accounts opened via V-CIP must be operational only after a concurrent audit to ensure process integrity [2] (27.xiv).  
-3. **Data Storage**: V-CIP records, including video recordings, must be stored in India with secure, timestamped storage [2] (27.iii).  
-4. **Digital KYC Limits**: For Aadhaar OTP-based non-face-to-face KYC, aggregate deposit balances cannot exceed ₹1 lakh, and credits cannot exceed ₹2 lakh annually [3] (25.3-4). Borrowal accounts are limited to term loans of ₹60,000 yearly [3] (25.5).  
-5. **Account Closure**: If CDD is not completed within one year, deposit accounts are closed immediately, and borrowal accounts stop further debits [3] (25.7).  
-6. **No Duplicate OTP Accounts**: The NBFC must declare that no other accounts are opened via OTP-based KYC with other REs [3] (25.8).  
-7. **Periodic KYC Updates**: V-CIP can be used for periodic KYC, but must follow [2] (27) and [1] (42.iii) rules, including Aadhaar OTP-based updates without [25] conditions.  
-8. **PAN Verification**: During periodic KYC, the NBFC must verify PAN details from the issuing authority’s database [1] (1.5.iii).  
-9. **Acknowledgment and Records**: The NBFC must provide customers with acknowledgment of document receipt and update records promptly [1] (1.5.iv).  
-10. **Customer Acceptance Policy**: The NBFC must avoid fictitious accounts, verify PAN/GST, and ensure customers are not on sanctions lists [4] (17.1-12).  
-11. **Risk-Based Approach**: Periodic KYC must adopt a risk-based strategy, with internal policies specifying exceptions like requiring physical presence or branch-specific updates [1] (1.5.vi).  
-These conditions apply universally, without differentiation for Middle Layer NBFCs.</t>
+          <t>The conditions applicable to your Middle Layer NBFC onboarding customers via video KYC (V-CIP) are as follows:  
+1. **Data Storage**: V-CIP records and video recordings must be stored in India, securely with timestamps for historical reference [2].  
+2. **Concurrent Audit**: Accounts opened via V-CIP must be operational only after concurrent audit to ensure process integrity [2].  
+3. **Identity Verification**: The NBFC must ensure the customer’s photograph in Aadhaar/OVD matches the one during V-CIP, and Aadhaar/PAN details align with the customer’s provided information [2].  
+4. **Activity Logs**: Preserve logs of V-CIP activities along with credentials of the official conducting the process [2].  
+5. **CDD for New Customers**: V-CIP can be used for CDD of new individual customers, proprietorship firms (with equivalent e-documents), and Legal Entities (LEs) [5].  
+6. **Periodic KYC Updates**: V-CIP may be used for periodic KYC updation of eligible customers [5].  
+7. **Account Limits**: For deposit/borrowal accounts opened via V-CIP, aggregate balances and credits must not exceed ₹1 lakh and ₹2 lakh respectively, and accounts must be closed if limits are breached [3].  
+8. **One-Year Restriction**: Accounts opened via V-CIP cannot operate beyond one year without completing CDD per paragraph 23 or V-CIP procedures [3].  
+9. **KYC Compliance**: Adhere to PMLA, 2002 guidelines and RBI’s KYC directives, including PAN verification and risk-based periodic updation [1][6].  
+10. **Documentation**: Provide customers with acknowledgment of KYC updates and ensure records are promptly updated in the NBFC’s database [1].  
+These conditions are explicitly outlined in the provided context passages.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3150,7 +3102,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>18.7</v>
+        <v>15.4</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3185,28 +3137,19 @@
       <c r="F49" t="inlineStr">
         <is>
           <t>The statutory auditor rules for a Middle Layer NBFC with over ₹1,000 crore assets are as follows:  
-1. **Audit Firm Requirements**:  
-   - If the NBFC’s asset size is **above ₹15,000 crore**, it must conduct statutory audits under **joint audit** by a **minimum of two audit firms** [1]. These firms must not share common partners or belong to the same audit network [1].  
-   - For NBFCs with asset sizes **between ₹1,000 crore and ₹15,000 crore**, the number of statutory auditors (SCAs/SAs) is capped based on asset size:  
-     - Up to ₹5,00,000 crore: **Maximum 4 SCAs/SAs** [1].  
-     - Above ₹5,00,000 crore and up to ₹10,00,000 crore: **Maximum 6 SCAs/SAs** [1].  
-     - Above ₹10,00,000 crore and up to ₹20,00,000 crore: **Maximum 8 SCAs/SAs** [1].  
-     - Above ₹20,00,000 crore: **Maximum 12 SCAs/SAs** [1].  
-2. **Eligibility Criteria for Auditors**:  
-   - For asset sizes **above ₹15,000 crore**, the audit firm must have:  
-     - Minimum **5 full-time partners (FTPs)** with at least 3 years of association [6].  
-     - Minimum **4 FCA partners** among FTPs [6].  
-     - Minimum **2 CISA/ISA qualified professionals** [6].  
-     - Minimum **15 years of audit experience** [6].  
-     - Minimum **18 professional staff** [6].  
-   - For asset sizes **between ₹1,000 crore and ₹15,000 crore**, the requirements are proportionally lower (e.g., 3 FTPs, 2 FCA partners, etc.) [6].  
-3. **Branch Audit Coverage**:  
-   - The NBFC must audit **at least the top 20 branches** (or top 20% of branches if fewer than 100) based on outstanding advances, ensuring coverage of **15% of total gross advances** [1].  
-   - Adherence to **Section 143(8) of the Companies Act, 2013** for branch audit procedures is mandatory [1].  
-4. **Exemptions and Exceptions**:  
-   - If the NBFC’s asset size falls **below ₹1,000 crore**, it may continue with existing procedures [5].  
-   - For **Unregistered Type I NBFCs** (not availing public funds or having customer interface), additional rules apply, including registration requirements and exception reports [4].  
-These rules apply unless the NBFC’s asset size exceeds ₹15,000 crore, in which case stricter joint audit requirements take effect [1].</t>
+1. **Number of SCAs/SAs**: The NBFC must appoint a minimum of one audit firm for statutory audit. However, if the asset size exceeds ₹15,000 crore, the NBFC must ensure statutory audit is conducted under joint audit by a minimum of two audit firms [1]. The maximum number of SCAs/SAs depends on the asset size:  
+   - Up to ₹5,00,000 crore: Maximum 4 SCAs/SAs [1].  
+   - Above ₹5,00,000 crore and up to ₹10,00,000 crore: Maximum 6 SCAs/SAs [1].  
+   - Above ₹10,00,000 crore and up to ₹20,00,000 crore: Maximum 8 SCAs/SAs [1].  
+   - Above ₹20,00,000 crore: Maximum 12 SCAs/SAs [1].  
+2. **Branch Audit Requirements**: The SCAs/SAs must audit at least the top 20 branches (or top 20% of branches if the NBFC has fewer than 100 branches) based on outstanding advances, ensuring coverage of at least 15% of total gross advances. Additionally, adherence to Section 143(8) of the Companies Act, 2013, for branch audits is mandatory [1].  
+3. **Eligibility Criteria for Auditors**:  
+   - For NBFCs with asset size above ₹15,000 crore: Minimum 5 full-time partners (FTPs), 4 FCA partners, 2 CISA/ISA qualified professionals, 15 years of audit experience, and 18 professional staff [6].  
+   - For NBFCs with asset size above ₹1,000 crore but below ₹15,000 crore: Minimum 3 FTPs, 2 FCA partners, 1 CISA/ISA qualified professional, 8 years of audit experience, and 12 professional staff [6].  
+   - For NBFCs with asset size up to ₹1,000 crore: Minimum 2 FTPs, 1 FCA partner, 1 CISA/ISA qualified professional, 6 years of audit experience, and 8 professional staff [6].  
+4. **Joint Auditor Restrictions**: The joint auditors must not share common partners or belong to the same audit network (as defined in Rule 6(3) of the Companies (Audit and Auditors) Rules, 2014) [1].  
+5. **Audit Firm Allocation**: The NBFC must finalize work allocation among SCAs/SAs before the audit commencement, in consultation with the auditors [1].  
+If the NBFC’s asset size exceeds ₹15,000 crore, it must comply with the joint audit requirements [1].</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3225,7 +3168,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>19.4</v>
+        <v>23.6</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3259,14 +3202,18 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>The borrower is classified as a Special Mention Account (SMA-2) because the overdue period of 65 days falls within the SMA-2 category (more than 60 days and up to 90 days) as per paragraph 23 of passage [5]. 
-**Conditions and exceptions**:  
-- **SMA-0**: Up to 30 days overdue.  
-- **SMA-1**: More than 30 days but up to 60 days overdue.  
-- **SMA-2**: More than 60 days but up to 90 days overdue [5].  
-- If the overdue period exceeds 90 days, the asset would be classified as a Non-Performing Asset (NPA) under paragraph 51 of passage [1] (for NBFC-ML).  
-- The classification is based on the day-end process, with the SMA/NPA date reflecting the calendar date of the day-end process [19].  
-- NBFCs must report SMA status to CRILC for borrowers with aggregate exposure of ₹5 crore and above [20].</t>
+          <t>The borrower's account is classified as **SMA-2** (Special Mention Account-2) because it is overdue for **65 days**, which falls within the 61–90 day range for SMA-2 classification [5]. 
+### Key conditions and requirements:
+1. **SMA Classification**:  
+   - **SMA-2** applies to accounts overdue **more than 60 days and up to 90 days** [5].  
+   - Classification is done as part of the **day-end process** for the relevant date, with the SMA date reflecting the calendar date of the day-end process [19].  
+2. **NPA Threshold**:  
+   - For Middle Layer NBFCs, **NPA classification** occurs only if the overdue period exceeds **90 days** [1][4]. Since the borrower is 65 days overdue, it does **not qualify as NPA**.  
+3. **Reporting Obligations**:  
+   - If the borrower’s aggregate exposure is **₹5 crore or more**, the NBFC must report the SMA status to **CRILC** monthly [20].  
+4. **Provisioning and Supervision**:  
+   - If the account transitions to NPA (e.g., after 90 days), the NBFC must apply **accelerated provisioning** and report to CRILC [22].  
+No other classifications apply at this stage.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3276,16 +3223,16 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>found 90days, 5crore; missing 61</t>
+          <t>all key figures present (61, 90days, 5crore)</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3319,19 +3266,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>The provisions applicable to your Middle Layer NBFC moving its loan management system to a cloud vendor include:  
-1. **Chapter IV and IT-specific provisions in Chapter II** of the Directions (as per [1][5][6]), which apply to NBFCs in Middle layer and above.  
-2. **Cloud-specific requirements** under F.4 of the Directions:  
-   - Undertake a business technology risk assessment to determine cloud adoption extent [2][3].  
-   - Ensure the IT outsourcing policy covers the entire data lifecycle (generation to deletion) and aligns with legal/regulatory requirements [2][3].  
-   - Address cloud-specific risks like multi-tenancy, data multilocality, and implement shared responsibility model-based security controls (e.g., NIST SP 800-210) [2][3].  
-   - Establish cloud governance with a documented policy, including data sovereignty compliance, stakeholder protection, and CSP due diligence [2][3].  
-   - Select CSPs based on risk assessment, ensuring enforceability of agreements and jurisdictional alignment [2][3].  
-   - Secure cloud architecture with encryption key control, data integrity protections, and resilience mechanisms [2][3].  
-   - Implement IAM with role-based access, segregation of duties, "least privilege," and multi-factor authentication [2][3].  
-   - Ensure cloud security controls meet or exceed on-premises standards, including secure network configurations and change authorization [2][3].  
-   - Define monitoring requirements, assess CSP’s cybersecurity capabilities, and validate subcontractor controls [2][3].  
-**Exceptions**: These Directions **do not apply** to NOFHCs or Type I NBFCs [1][5][6]. For credit card-related outsourcing, additional provisions from the RBI’s Credit Cards Directions also apply [1].</t>
+          <t>The provisions in **Chapter IV** and **IT-specific provisions in Chapter II** of the Directions apply to your Middle Layer NBFC, as these are explicitly stated to be applicable for NBFCs in Middle layer and above layers [1]. Additionally, the **cloud computing usage requirements** in **F.4** (sections 96–97) apply to your NBFC, as moving loan management systems to a cloud vendor involves outsourcing financial services [4]. These requirements include:  
+1. **Comprehensive assessment** of business strategy, IT applications, and cloud-related expenditures (e.g., migration, integration, and recurring costs) [2].  
+2. **IT outsourcing policy** covering the entire data lifecycle (generation, cloud entry, and deletion) and alignment with legal/regulatory requirements [2].  
+3. **Risk management framework** addressing cloud-specific factors like multi-tenancy, data location, and attendant risks [2].  
+4. **Cloud security controls** based on the shared responsibility model, including reference to NIST SP 800-210 for best practices [2].  
+5. **Cloud governance** with a documented policy addressing:  
+   - Identifying cloud-movable services [3].  
+   - Protecting stakeholder interests and regulatory compliance (privacy, data sovereignty, etc.) [3].  
+   - Due diligence for CSPs and risk assessments for CSP selection [3].  
+6. **Technology architecture** standards: secure container-based data management, data integrity/confidentiality protections, and resilience for cloud recovery [3].  
+7. **Identity and Access Management (IAM)** with role-based access, segregation of duties, and multi-factor authentication [3].  
+8. **Security controls** ensuring cloud-based applications meet or exceed on-premises security objectives, including network security, asset monitoring, and change authorization [3].  
+9. **Monitoring requirements** for CSPs, including testing frequency, subcontractor assessments, and log integration with your SOC [3].  
+These obligations are in addition to the general applicability of the Directions to Middle Layer NBFCs [1][5].</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3350,7 +3298,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3384,7 +3332,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify SEBI LODR disclosure timelines for listed NCDs. The references to SEBI LODR in the passages relate to corporate governance disclosures in annual reports [2] and currency futures disclosures [5], but none address timelines for NCD-specific disclosures. Further details would require consulting the full SEBI LODR regulations.</t>
+          <t>The provided passages do not specify SEBI LODR disclosure timelines for listed NCDs. While SEBI LODR regulations (e.g., Schedule V of the 2015 LODR Regulations) mandate disclosures in annual reports for corporate governance [2], no explicit timelines for NCD-related disclosures are outlined in the context. Additionally, passage [1] mentions reporting secondary market OTC trades within 15 minutes of execution but does not link this to LODR disclosure timelines for NCDs. Thus, the answer cannot be derived from the given texts.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3403,7 +3351,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>6.8</v>
+        <v>10.1</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3437,7 +3385,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The provided passages do not specify SEBI's requirements for a debenture trustee in public NCD issues. The context focuses on regulations related to investments, public deposits, private placements, and exemptions, but does not address SEBI's mandates for debenture trustees. For example, [1] mentions SEBI's guidelines on corporate debt securities [133], and [2] discusses NBFC compliance with RBI directions [2.3], but neither references debenture trustees. Thus, no direct answer is available from the given passages.</t>
+          <t>The provided passages do not specify SEBI's requirements for a debenture trustee in relation to public NCD issues. The contexts primarily address regulations by the Reserve Bank of India (RBI) and SEBI's exemptions in specific scenarios, but none directly outline SEBI's mandates for debenture trustees in public NCD offerings.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3456,7 +3404,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3490,7 +3438,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The passages do not specify a maximum number of insurers that an IRDAI corporate agent can tie up with. The conditions outlined focus on operational requirements such as avoiding restrictive practices, ensuring voluntary customer choice, and non-linkage between financial services and insurance products [1], [3]. No limit on the number of insurers is mentioned in the provided contexts.</t>
+          <t>The provided passages do not specify the maximum number of insurers that can be tied up with as an IRDAI corporate agent. The conditions outlined in [1], [3], and [5] focus on compliance requirements, restrictions on customer choice, and operational guidelines for agencies, but none mention a numerical limit on the number of insurers. Therefore, the answer cannot be determined from the given contexts.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3509,7 +3457,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3543,11 +3491,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The TDS threshold on interest paid to depositors is not specified in the provided passages. The context does not mention any specific threshold for TDS (Tax Deducted at Source) applicable to interest payments to depositors. 
-Conditions and exceptions from the passages:  
-- The passages focus on interest rate ceilings (e.g., 12.5% p.a. for NBFCs [3]), interest payment mechanisms [1], and asset-liability management [2][4][6], but none address TDS thresholds or tax deduction rules.  
-- No mention of TDS rates, thresholds, or related provisions is found in the numbered contexts.  
-Answer: The provided passages do not contain information about the TDS threshold on interest paid to depositors.</t>
+          <t>The passages do not provide information about the TDS (Tax Deducted at Source) threshold on interest paid to depositors. No mention of TDS thresholds, rates, or related provisions is found in the provided contexts.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3557,16 +3501,16 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>correctly declined to answer</t>
+          <t>answered a question the corpus should not cover - check for invention</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3600,7 +3544,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The context passages do not specify the exact GST rate applicable to loan processing fees. However, they mention that NBFCs must follow instructions from the Central Board of Indirect Taxes &amp; Customs (CBIC) regarding the applicability of GST on penal charges [1](iv). For loan processing fees, the GST rate would depend on CBIC's guidelines, which are not detailed in the provided passages.</t>
+          <t>The provided passages do not specify the exact GST rate applicable to loan processing fees. However, they mention that NBFCs must follow instructions from the Central Board of Indirect Taxes &amp; Customs (CBIC) regarding the applicability of GST on penal charges [1](iv). For loan processing fees, the GST rate would depend on CBIC's guidelines, which are not detailed in the given contexts.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3619,7 +3563,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3653,7 +3597,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>No, there is no requirement mentioned in the provided passages to spend 2% of profits on CSR. The contexts discuss prudential norms, dividend payout ratios, capital adequacy, and related party disclosures, but none reference CSR obligations or percentage allocations of profits for such purposes.</t>
+          <t>The passages do not contain any information regarding a requirement to spend 2% of profits on CSR. The provided contexts focus on regulatory guidelines for NBFCs, dividend payout ratios, prudential norms, related party disclosures, concentration risk management, and asset classification, but none mention CSR obligations or specific profit allocation percentages for such purposes.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3663,16 +3607,16 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3706,7 +3650,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The passages do not specify a deadline for holding the annual general meeting (AGM). They only mention submission deadlines for financial statements and other documents **after** the AGM is held (e.g., within 15 days of the meeting [1][2], or within 21 days of the Reference Date for yearly returns [4]). No rule in the contexts directly ties the AGM's holding date to a specific timeline.</t>
+          <t>The passages do not specify a deadline for holding the annual general meeting (AGM). They only mention that certain documents, such as financial statements and reports, must be submitted to regulatory authorities within **15 days of the AGM** [1], [2]. The exact date or timeline for holding the AGM itself is not provided in the context.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3725,7 +3669,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3759,7 +3703,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The provided context passages do not contain any information regarding the closure of trading windows for insiders before results.</t>
+          <t>The provided passages do not contain any information regarding the timing of trading windows for insiders before results. The contexts cover topics such as G-Sec trading regulations [1], interest rate risk measurement [2], asset restructuring [3], credit reporting formats [4], supervisory returns [5], and related party disclosures [6], but none address insider trading restrictions or pre-results trading windows.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3778,7 +3722,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3812,7 +3756,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The passages do not mention any commission rates or rules related to group credit-life insurance sold with loans. No specific figures, regulations, or conditions about such commissions are provided in the context.</t>
+          <t>The passages do not provide information about commissions earned on group credit-life insurance sold with loans.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3822,16 +3766,16 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>correctly declined to answer</t>
+          <t>answered a question the corpus should not cover - check for invention</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3865,7 +3809,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention anything about tax deductions for NPA provisions. They focus on provisioning requirements, asset classification, and regulatory guidelines for NBFCs, but none address tax treatment or deductibility of provisions related to NPAs. Therefore, no claim about tax deductions can be made based on the given information.</t>
+          <t>The passages do not provide information on whether NPA provisions can be claimed as a tax deduction. The content focuses on provisioning norms, asset classification, and disclosure requirements but does not address tax treatment or deductibility of provisions.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3884,7 +3828,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>

--- a/eval/nbfc_retrieval_test_questions_results_v2.xlsx
+++ b/eval/nbfc_retrieval_test_questions_results_v2.xlsx
@@ -2103,12 +2103,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>no numeric facts to compare - read the answer yourself</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>no numeric facts to compare - read the answer yourself</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J60" t="n">
